--- a/WorkBot/main/data/order_archive/A.L. George/A.L. George_Collegetown_20260724.xlsx
+++ b/WorkBot/main/data/order_archive/A.L. George/A.L. George_Collegetown_20260724.xlsx
@@ -491,13 +491,13 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D6" t="n">
         <v>26</v>
       </c>
       <c r="E6" t="n">
-        <v>52</v>
+        <v>78</v>
       </c>
     </row>
     <row r="7">
